--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484247_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484247_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0852</v>
+        <v>6.3872</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0787</v>
+        <v>3.7347</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0066</v>
+        <v>2.6525</v>
       </c>
       <c r="G2" t="n">
         <v>5.6124</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9882</v>
+        <v>0.2902</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5752</v>
+        <v>0.2312</v>
       </c>
       <c r="U2" t="n">
-        <v>0.413</v>
+        <v>0.059</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2735</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3456</v>
+        <v>4.3392</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6183</v>
+        <v>1.0204</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7273</v>
+        <v>3.3188</v>
       </c>
       <c r="G3" t="n">
         <v>1.0857</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8106</v>
+        <v>1.8042</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5963</v>
+        <v>1.9984</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2143</v>
+        <v>-0.1942</v>
       </c>
       <c r="V3" t="n">
         <v>0.2772</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9515</v>
+        <v>4.1815</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8328</v>
+        <v>2.9538</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1187</v>
+        <v>1.2277</v>
       </c>
       <c r="G4" t="n">
         <v>1.8905</v>
@@ -766,13 +766,13 @@
         <v>2.3441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3698</v>
+        <v>0.5998</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8861</v>
+        <v>1.0072</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5163</v>
+        <v>-0.4074</v>
       </c>
       <c r="V4" t="n">
         <v>1.4959</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9651</v>
+        <v>2.2959</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8617</v>
+        <v>0.0531</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1033</v>
+        <v>2.2428</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1733</v>
+        <v>0.5704</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8631</v>
+        <v>-0.3599</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3101</v>
+        <v>0.9303</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0433</v>
+        <v>0.0511</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0028</v>
+        <v>-0.6102</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>0.6613</v>
       </c>
       <c r="M5" t="n">
-        <v>0.13</v>
+        <v>0.5193</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1397</v>
+        <v>0.2502</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2696</v>
+        <v>0.269</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0104</v>
+        <v>0.3116</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1816</v>
+        <v>0.1508</v>
       </c>
       <c r="U5" t="n">
-        <v>0.192</v>
+        <v>0.1608</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5392</v>
+        <v>1.9106</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.513</v>
+        <v>0.8617</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0522</v>
+        <v>1.0489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5704</v>
+        <v>1.1733</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3599</v>
+        <v>0.8631</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9303</v>
+        <v>0.3101</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0511</v>
+        <v>1.0433</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6102</v>
+        <v>1.0028</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6613</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5193</v>
+        <v>0.13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2502</v>
+        <v>-0.1397</v>
       </c>
       <c r="O6" t="n">
-        <v>0.269</v>
+        <v>0.2696</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4452</v>
+        <v>-0.044</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4153</v>
+        <v>-0.1816</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0298</v>
+        <v>0.1375</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2934</v>
+        <v>1.6038</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5179</v>
+        <v>-1.4691</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8113</v>
+        <v>3.0729</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3966</v>
+        <v>-1.3006</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9112</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4854</v>
+        <v>-0.7951</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7972</v>
+        <v>-2.075</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7163</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0809</v>
+        <v>-1.4686</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5994</v>
+        <v>0.7743</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1949</v>
+        <v>0.1008</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4045</v>
+        <v>0.6735</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>3.1255</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3076</v>
+        <v>0.0998</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3026</v>
+        <v>0.9267</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.005</v>
+        <v>-0.827</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7731</v>
+        <v>1.8279</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.9917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2947</v>
+        <v>-0.0311</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9046</v>
+        <v>-1.9085</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6099</v>
+        <v>1.8773</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3006</v>
+        <v>-0.2155</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5054999999999999</v>
+        <v>1.2267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7951</v>
+        <v>-1.4422</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.075</v>
+        <v>-1.0096</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6064000000000001</v>
+        <v>1.1064</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4686</v>
+        <v>-2.1161</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7743</v>
+        <v>0.7942</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1008</v>
+        <v>0.1203</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6735</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-2.1488</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3.1255</v>
-      </c>
       <c r="S8" t="n">
-        <v>-1.7988</v>
+        <v>0.1025</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5088</v>
+        <v>-0.2812</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.29</v>
+        <v>0.3837</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8279</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5095</v>
+        <v>-0.1449</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.414</v>
+        <v>-2.4622</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9046</v>
+        <v>2.3173</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2155</v>
+        <v>0.6014</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2267</v>
+        <v>0.5199</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4422</v>
+        <v>0.0815</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0096</v>
+        <v>-0.1134</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1064</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1161</v>
+        <v>-0.7274</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7942</v>
+        <v>0.7148</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1203</v>
+        <v>-0.0941</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.8089</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3759</v>
+        <v>0.0351</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.5813</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4109</v>
+        <v>-0.5463</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.651</v>
+        <v>-0.1784</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8866</v>
+        <v>1.5784</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2356</v>
+        <v>-1.7568</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6014</v>
+        <v>1.3966</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5199</v>
+        <v>0.9112</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0815</v>
+        <v>0.4854</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1134</v>
+        <v>0.7972</v>
       </c>
       <c r="K10" t="n">
-        <v>0.614</v>
+        <v>0.7163</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7274</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7148</v>
+        <v>0.5994</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0941</v>
+        <v>0.1949</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8089</v>
+        <v>0.4045</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.471</v>
+        <v>-0.1926</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1569</v>
+        <v>-0.2421</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.628</v>
+        <v>0.0495</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.7731</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.9917</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7548</v>
+        <v>-0.8609</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0268</v>
+        <v>-2.3508</v>
       </c>
       <c r="F11" t="n">
-        <v>1.272</v>
+        <v>1.4899</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4711</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.8289</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3841</v>
+        <v>1.0601</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4491</v>
+        <v>-0.2312</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1841</v>
+        <v>-1.3959</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1997</v>
+        <v>-0.472</v>
       </c>
       <c r="G12" t="n">
         <v>0.82</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2145</v>
+        <v>0.0027</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3026</v>
+        <v>-0.2421</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5172</v>
+        <v>0.2448</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8279</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.1991</v>
+        <v>18.107</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1800000000000005</v>
+        <v>1.0876</v>
       </c>
       <c r="F13" t="n">
-        <v>17.0192</v>
+        <v>17.0193</v>
       </c>
       <c r="G13" t="n">
-        <v>9.163100000000002</v>
+        <v>9.1631</v>
       </c>
       <c r="H13" t="n">
-        <v>7.812900000000002</v>
+        <v>7.8129</v>
       </c>
       <c r="I13" t="n">
         <v>1.3502</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9926</v>
+        <v>2.992600000000001</v>
       </c>
       <c r="K13" t="n">
         <v>7.0322</v>
@@ -1453,13 +1453,13 @@
         <v>6.170500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7803999999999999</v>
+        <v>0.7804</v>
       </c>
       <c r="O13" t="n">
         <v>5.3898</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8836</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.6741</v>
@@ -1468,10 +1468,10 @@
         <v>18.5576</v>
       </c>
       <c r="S13" t="n">
-        <v>2.93</v>
+        <v>3.8382</v>
       </c>
       <c r="T13" t="n">
-        <v>4.1009</v>
+        <v>5.008700000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-1.1708</v>
@@ -1480,7 +1480,7 @@
         <v>0.2223000000000002</v>
       </c>
       <c r="W13" t="n">
-        <v>6.760199999999999</v>
+        <v>6.7602</v>
       </c>
       <c r="X13" t="n">
         <v>-6.537699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7188</v>
+        <v>1.8918</v>
       </c>
       <c r="E14" t="n">
-        <v>2.43</v>
+        <v>1.1156</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2888</v>
+        <v>0.7763</v>
       </c>
       <c r="G14" t="n">
         <v>0.7231</v>
@@ -1546,13 +1546,13 @@
         <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4413</v>
+        <v>0.6143</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9096</v>
+        <v>0.5951</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4683</v>
+        <v>0.0192</v>
       </c>
       <c r="V14" t="n">
         <v>0.5545</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2686</v>
+        <v>1.8197</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0447</v>
+        <v>1.9697</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2239</v>
+        <v>-0.15</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4021</v>
+        <v>2.0616</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3758</v>
+        <v>0.9967</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7779</v>
+        <v>1.0649</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7669</v>
+        <v>2.7104</v>
       </c>
       <c r="K15" t="n">
-        <v>0.472</v>
+        <v>2.0491</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2949</v>
+        <v>0.6613</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6353</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8478</v>
+        <v>-1.0524</v>
       </c>
       <c r="O15" t="n">
-        <v>1.483</v>
+        <v>0.4037</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.3674</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6024</v>
+        <v>-0.681</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3548</v>
+        <v>-0.2598</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2476</v>
+        <v>-0.4212</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>0.2437</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6642</v>
+        <v>-0.6428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6737</v>
+        <v>1.6342</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9586</v>
+        <v>0.2469</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2848</v>
+        <v>1.3873</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0616</v>
+        <v>2.4021</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9967</v>
+        <v>-0.3758</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0649</v>
+        <v>2.7779</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7104</v>
+        <v>1.7669</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0491</v>
+        <v>0.472</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6613</v>
+        <v>1.2949</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6487000000000001</v>
+        <v>0.6353</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0524</v>
+        <v>-0.8478</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4037</v>
+        <v>1.483</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.3674</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.827</v>
+        <v>-1.2368</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.271</v>
+        <v>-0.1526</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.556</v>
+        <v>-1.0842</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2437</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6428</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6882</v>
+        <v>0.1078</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7057</v>
+        <v>-1.099</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0175</v>
+        <v>1.2068</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9199000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9404</v>
+        <v>-0.1444</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6657</v>
+        <v>-0.0591</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2746</v>
+        <v>-0.0854</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5092</v>
+        <v>-2.3565</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.1956</v>
+        <v>-2.9175</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6864</v>
+        <v>0.5609</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3165</v>
+        <v>-2.6481</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5733</v>
+        <v>-2.6337</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2568</v>
+        <v>-0.0144</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8765</v>
+        <v>-2.6684</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0553</v>
+        <v>-2.1157</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8212</v>
+        <v>-0.5527</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.0203</v>
       </c>
       <c r="N18" t="n">
         <v>-0.518</v>
       </c>
       <c r="O18" t="n">
-        <v>1.078</v>
+        <v>0.5383</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.3208</v>
+        <v>-2.3441</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.345</v>
+        <v>-0.6163</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0018</v>
+        <v>0.2671</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.8834</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3656</v>
+        <v>0.9079</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3656</v>
+        <v>-0.9201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8985</v>
+        <v>-3.1275</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9175</v>
+        <v>-0.9048</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0189</v>
+        <v>-2.2227</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6481</v>
+        <v>-1.4009</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.6337</v>
+        <v>0.5815</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0144</v>
+        <v>-1.9824</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6684</v>
+        <v>-0.0376</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1157</v>
+        <v>1.2701</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5527</v>
+        <v>-1.3077</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0203</v>
+        <v>-1.3634</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.518</v>
+        <v>-0.6887</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5383</v>
+        <v>-0.6747</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3441</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1583</v>
+        <v>0.053</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2671</v>
+        <v>0.1095</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4254</v>
+        <v>-0.0565</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9079</v>
+        <v>-1.5842</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9201</v>
+        <v>-1.5842</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2558</v>
+        <v>-3.1458</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.006</v>
+        <v>-4.8022</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2499</v>
+        <v>1.6564</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4009</v>
+        <v>-1.3165</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5815</v>
+        <v>-1.5733</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9824</v>
+        <v>0.2568</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0376</v>
+        <v>-1.8765</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2701</v>
+        <v>-1.0553</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3077</v>
+        <v>-0.8212</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3634</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6887</v>
+        <v>-0.518</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6747</v>
+        <v>1.078</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-3.3208</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.2917</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0083</v>
+        <v>0.3951</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0837</v>
+        <v>-0.6867</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5842</v>
+        <v>-0.3656</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5842</v>
+        <v>-0.3656</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7448</v>
+        <v>-3.4687</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0327</v>
+        <v>-1.7293</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7121</v>
+        <v>-1.7394</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0697</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1392</v>
+        <v>0.1369</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U21" t="n">
-        <v>0.345</v>
+        <v>0.3177</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3405</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3658</v>
+        <v>-3.9147</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9341</v>
+        <v>-3.4285</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4317</v>
+        <v>-0.4862</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0088</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1849</v>
+        <v>0.2662</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6052</v>
+        <v>-0.0997</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4203</v>
+        <v>0.3658</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3979</v>
+        <v>-5.2912</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6611</v>
+        <v>-5.47</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2632</v>
+        <v>0.1788</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9858</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2111</v>
+        <v>0.3177</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3649</v>
+        <v>0.556</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1538</v>
+        <v>-0.2382</v>
       </c>
       <c r="V23" t="n">
         <v>0.6977</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.1991</v>
+        <v>-15.8509</v>
       </c>
       <c r="E24" t="n">
-        <v>-17.0194</v>
+        <v>-17.0191</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1797999999999998</v>
+        <v>1.1682</v>
       </c>
       <c r="G24" t="n">
         <v>-9.1629</v>
@@ -2326,13 +2326,13 @@
         <v>13.6741</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.930099999999999</v>
+        <v>-1.582100000000001</v>
       </c>
       <c r="T24" t="n">
         <v>1.1708</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.1009</v>
+        <v>-2.7529</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2222999999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484247_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484247_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2959</v>
+        <v>1.9106</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0531</v>
+        <v>0.8617</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2428</v>
+        <v>1.0489</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5704</v>
+        <v>1.1733</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3599</v>
+        <v>0.8631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9303</v>
+        <v>0.3101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0511</v>
+        <v>1.0433</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6102</v>
+        <v>1.0028</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6613</v>
+        <v>0.0405</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5193</v>
+        <v>0.13</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2502</v>
+        <v>-0.1397</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269</v>
+        <v>0.2696</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3116</v>
+        <v>-0.044</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1508</v>
+        <v>-0.1816</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1608</v>
+        <v>0.1375</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9106</v>
+        <v>1.6038</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8617</v>
+        <v>-1.4691</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0489</v>
+        <v>3.0729</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1733</v>
+        <v>-1.3006</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8631</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3101</v>
+        <v>-0.7951</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0433</v>
+        <v>-2.075</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0028</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-1.4686</v>
       </c>
       <c r="M6" t="n">
-        <v>0.13</v>
+        <v>0.7743</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1397</v>
+        <v>0.1008</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2696</v>
+        <v>0.6735</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>3.1255</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.044</v>
+        <v>0.0998</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1816</v>
+        <v>0.9267</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1375</v>
+        <v>-0.827</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6038</v>
+        <v>1.521</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4691</v>
+        <v>1.521</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0729</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3006</v>
+        <v>1.521</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7951</v>
+        <v>1.214</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.075</v>
+        <v>1.521</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6064000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4686</v>
+        <v>1.214</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7743</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1008</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6735</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0998</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9267</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.827</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0311</v>
+        <v>0.775</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9085</v>
+        <v>-1.4678</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8773</v>
+        <v>2.2428</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2155</v>
+        <v>-0.9506</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2267</v>
+        <v>-0.6669</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4422</v>
+        <v>-0.2837</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0096</v>
+        <v>-1.4699</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1064</v>
+        <v>-0.9171</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.1161</v>
+        <v>-0.5527</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7942</v>
+        <v>0.5193</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1203</v>
+        <v>0.2502</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1025</v>
+        <v>0.3116</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2812</v>
+        <v>0.1508</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3837</v>
+        <v>0.1608</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1449</v>
+        <v>0.307</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4622</v>
+        <v>0.307</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3173</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6014</v>
+        <v>0.307</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5199</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0815</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1134</v>
+        <v>0.307</v>
       </c>
       <c r="K9" t="n">
-        <v>0.614</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7274</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7148</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0941</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8089</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0351</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5813</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1784</v>
+        <v>-0.0311</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5784</v>
+        <v>-1.9085</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7568</v>
+        <v>1.8773</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3966</v>
+        <v>-0.2155</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9112</v>
+        <v>1.2267</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4854</v>
+        <v>-1.4422</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7972</v>
+        <v>-1.0096</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7163</v>
+        <v>1.1064</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0809</v>
+        <v>-2.1161</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5994</v>
+        <v>0.7942</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1949</v>
+        <v>0.1203</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4045</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1926</v>
+        <v>0.1025</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2421</v>
+        <v>-0.2812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0495</v>
+        <v>0.3837</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7731</v>
+        <v>0.2772</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9917</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8609</v>
+        <v>-0.1449</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3508</v>
+        <v>-2.4622</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4899</v>
+        <v>2.3173</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4711</v>
+        <v>0.6014</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7992</v>
+        <v>0.5199</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6719</v>
+        <v>0.0815</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.7114</v>
+        <v>-0.1134</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7701</v>
+        <v>0.614</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9414</v>
+        <v>-0.7274</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2403</v>
+        <v>0.7148</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0291</v>
+        <v>-0.0941</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2694</v>
+        <v>0.8089</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8289</v>
+        <v>0.0351</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0601</v>
+        <v>0.5813</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2312</v>
+        <v>-0.5463</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3959</v>
+        <v>-0.1784</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9239000000000001</v>
+        <v>1.5784</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.472</v>
+        <v>-1.7568</v>
       </c>
       <c r="G12" t="n">
-        <v>0.82</v>
+        <v>1.3966</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.9112</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2158</v>
+        <v>0.4854</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4902</v>
+        <v>0.7972</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4093</v>
+        <v>0.7163</v>
       </c>
       <c r="L12" t="n">
         <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3298</v>
+        <v>0.5994</v>
       </c>
       <c r="N12" t="n">
         <v>0.1949</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1348</v>
+        <v>0.4045</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0027</v>
+        <v>-0.1926</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2448</v>
+        <v>0.0495</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8279</v>
+        <v>-1.7731</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.8279</v>
+        <v>-2.9917</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>Q. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,229 +1483,240 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.107</v>
+        <v>-0.8609</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0876</v>
+        <v>-2.3508</v>
       </c>
       <c r="F13" t="n">
-        <v>17.0193</v>
+        <v>1.4899</v>
       </c>
       <c r="G13" t="n">
-        <v>9.1631</v>
+        <v>-2.4711</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8129</v>
+        <v>-0.7992</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3502</v>
+        <v>-1.6719</v>
       </c>
       <c r="J13" t="n">
-        <v>2.992600000000001</v>
+        <v>-2.7114</v>
       </c>
       <c r="K13" t="n">
-        <v>7.0322</v>
+        <v>-0.7701</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0398</v>
+        <v>-1.9414</v>
       </c>
       <c r="M13" t="n">
-        <v>6.170500000000001</v>
+        <v>0.2403</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7804</v>
+        <v>-0.0291</v>
       </c>
       <c r="O13" t="n">
-        <v>5.3898</v>
+        <v>0.2694</v>
       </c>
       <c r="P13" t="n">
-        <v>4.883599999999999</v>
+        <v>0.7814</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6741</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>18.5576</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8382</v>
+        <v>0.8289</v>
       </c>
       <c r="T13" t="n">
-        <v>5.008700000000001</v>
+        <v>1.0601</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1708</v>
+        <v>-0.2312</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2223000000000002</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7602</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.537699999999999</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8918</v>
+        <v>-1.7029</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1156</v>
+        <v>-1.2309</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7763</v>
+        <v>-0.472</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7231</v>
+        <v>0.513</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4538</v>
+        <v>0.2973</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2692</v>
+        <v>0.2158</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9427</v>
+        <v>0.1833</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9427</v>
+        <v>0.1023</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2196</v>
+        <v>0.3298</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4889</v>
+        <v>0.1949</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2692</v>
+        <v>0.1348</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6143</v>
+        <v>0.0027</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5951</v>
+        <v>-0.2421</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0192</v>
+        <v>0.2448</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5545</v>
+        <v>-1.8279</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FRIVALCA LA MUELA</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8197</v>
+        <v>18.1071</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9697</v>
+        <v>1.0877</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.15</v>
+        <v>17.0193</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0616</v>
+        <v>9.1631</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9967</v>
+        <v>7.812900000000002</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0649</v>
+        <v>1.3502</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7104</v>
+        <v>2.992700000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0491</v>
+        <v>7.032299999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6613</v>
+        <v>-4.0398</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6487000000000001</v>
+        <v>6.170500000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0524</v>
+        <v>0.7803999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4037</v>
+        <v>5.3898</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>4.8836</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3674</v>
+        <v>-13.6741</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>18.5576</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.681</v>
+        <v>3.8382</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2598</v>
+        <v>5.0087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4212</v>
+        <v>-1.1708</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2437</v>
+        <v>0.2223000000000002</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>6.7602</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6428</v>
-      </c>
+        <v>-6.537699999999999</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6342</v>
+        <v>2.4419</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2469</v>
+        <v>2.4419</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3873</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4021</v>
+        <v>2.4419</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3758</v>
+        <v>1.2279</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7779</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7669</v>
+        <v>2.4419</v>
       </c>
       <c r="K16" t="n">
-        <v>0.472</v>
+        <v>1.2279</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2949</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6353</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8478</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.483</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2368</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1526</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0842</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. ULLO NARRO</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1078</v>
+        <v>1.8918</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.099</v>
+        <v>1.1156</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2068</v>
+        <v>0.7763</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0.7231</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0241</v>
+        <v>0.4538</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9439</v>
+        <v>0.2692</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0399</v>
+        <v>0.9427</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3083</v>
+        <v>0.9427</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3482</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1201</v>
+        <v>-0.2196</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2842</v>
+        <v>-0.4889</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4043</v>
+        <v>0.2692</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1444</v>
+        <v>0.6143</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0591</v>
+        <v>0.5951</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0854</v>
+        <v>0.0192</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3565</v>
+        <v>1.6342</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9175</v>
+        <v>0.2469</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5609</v>
+        <v>1.3873</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6481</v>
+        <v>2.4021</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6337</v>
+        <v>-0.3758</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0144</v>
+        <v>2.7779</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.6684</v>
+        <v>1.7669</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1157</v>
+        <v>0.472</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>1.2949</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0203</v>
+        <v>0.6353</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.518</v>
+        <v>-0.8478</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5383</v>
+        <v>1.483</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6163</v>
+        <v>-1.2368</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2671</v>
+        <v>-0.1526</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8834</v>
+        <v>-1.0842</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9079</v>
+        <v>0.6642</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9201</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>G. ULLO NARRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1275</v>
+        <v>0.1078</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9048</v>
+        <v>-1.099</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2227</v>
+        <v>1.2068</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4009</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5815</v>
+        <v>0.0241</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9824</v>
+        <v>-0.9439</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0376</v>
+        <v>-1.0399</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2701</v>
+        <v>0.3083</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3077</v>
+        <v>-1.3482</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3634</v>
+        <v>0.1201</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6887</v>
+        <v>-0.2842</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6747</v>
+        <v>0.4043</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.053</v>
+        <v>-0.1444</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1095</v>
+        <v>-0.0591</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0565</v>
+        <v>-0.0854</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5842</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5842</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1458</v>
+        <v>-0.6222</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8022</v>
+        <v>-0.4722</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6564</v>
+        <v>-0.15</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3165</v>
+        <v>-0.3803</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5733</v>
+        <v>-0.2312</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2568</v>
+        <v>-0.149</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8765</v>
+        <v>0.2685</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0553</v>
+        <v>0.8212</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8212</v>
+        <v>-0.5527</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.518</v>
+        <v>-1.0524</v>
       </c>
       <c r="O20" t="n">
-        <v>1.078</v>
+        <v>0.4037</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.3208</v>
+        <v>-1.3674</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2917</v>
+        <v>-0.681</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3951</v>
+        <v>-0.2598</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6867</v>
+        <v>-0.4212</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3656</v>
+        <v>0.2437</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3656</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4687</v>
+        <v>-2.3565</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7293</v>
+        <v>-2.9175</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7394</v>
+        <v>0.5609</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0697</v>
+        <v>-2.6481</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9908</v>
+        <v>-2.6337</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.079</v>
+        <v>-0.0144</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5718</v>
+        <v>-2.6684</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1023</v>
+        <v>-2.1157</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>-0.5527</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.498</v>
+        <v>0.0203</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0931</v>
+        <v>-0.518</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4049</v>
+        <v>0.5383</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-2.3441</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1369</v>
+        <v>-0.6163</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1808</v>
+        <v>0.2671</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3177</v>
+        <v>-0.8834</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.3405</v>
+        <v>0.9079</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3405</v>
+        <v>-0.9201</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9147</v>
+        <v>-3.1275</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4285</v>
+        <v>-0.9048</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4862</v>
+        <v>-2.2227</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0088</v>
+        <v>-1.4009</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6038</v>
+        <v>0.5815</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4051</v>
+        <v>-1.9824</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5941</v>
+        <v>-0.0376</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5941</v>
+        <v>1.2701</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.3077</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4148</v>
+        <v>-1.3634</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0097</v>
+        <v>-0.6887</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4051</v>
+        <v>-0.6747</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2662</v>
+        <v>0.053</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0997</v>
+        <v>0.1095</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3658</v>
+        <v>-0.0565</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.5842</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-1.5842</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. KIRIS</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2912</v>
+        <v>-3.1458</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.47</v>
+        <v>-4.8022</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1788</v>
+        <v>1.6564</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9858</v>
+        <v>-1.3165</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6915</v>
+        <v>-1.5733</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2943</v>
+        <v>0.2568</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.802</v>
+        <v>-1.8765</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1599</v>
+        <v>-1.0553</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6421</v>
+        <v>-0.8212</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1838</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5316</v>
+        <v>-0.518</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3478</v>
+        <v>1.078</v>
       </c>
       <c r="P23" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-3.3208</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-5.2743</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3177</v>
+        <v>-0.2917</v>
       </c>
       <c r="T23" t="n">
-        <v>0.556</v>
+        <v>0.3951</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2382</v>
+        <v>-0.6867</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6977</v>
+        <v>-0.3656</v>
       </c>
       <c r="W23" t="n">
-        <v>2.0503</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3527</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.4687</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.7293</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.7394</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.0697</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.9908</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.079</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.5718</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.498</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.0931</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1808</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.3405</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.3405</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F. VIDAL RAMOS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.9147</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.4285</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.4862</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.0088</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.6038</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.5941</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2.5941</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.4148</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.4051</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.0997</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. KIRIS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.2912</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.9858</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.6915</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.2943</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.802</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.1599</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2.6421</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.1838</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.5316</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.3478</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-5.2743</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.2382</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6977</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.0503</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.3527</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484247_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>-15.8509</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E27" t="n">
         <v>-17.0191</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F27" t="n">
         <v>1.1682</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G27" t="n">
         <v>-9.1629</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H27" t="n">
         <v>-7.812799999999999</v>
       </c>
-      <c r="I24" t="n">
-        <v>-1.3503</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="I27" t="n">
+        <v>-1.3502</v>
+      </c>
+      <c r="J27" t="n">
         <v>-6.170300000000001</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K27" t="n">
         <v>-0.7804999999999997</v>
       </c>
-      <c r="L24" t="n">
-        <v>-5.3898</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L27" t="n">
+        <v>-5.389800000000001</v>
+      </c>
+      <c r="M27" t="n">
         <v>-2.9926</v>
       </c>
-      <c r="N24" t="n">
-        <v>-7.0324</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N27" t="n">
+        <v>-7.032399999999999</v>
+      </c>
+      <c r="O27" t="n">
         <v>4.0396</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>-4.8835</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-18.5575</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>13.6741</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>-1.582100000000001</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T27" t="n">
         <v>1.1708</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>-2.7529</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-0.2222999999999999</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>6.5378</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X27" t="n">
         <v>-6.760300000000001</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
